--- a/data/trans_bre/IP2003-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 11,54</t>
+          <t>-3,31; 10,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 5,74</t>
+          <t>-9,15; 5,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 8,47</t>
+          <t>-3,94; 9,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 8,11</t>
+          <t>-23,84; 8,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 104,59</t>
+          <t>-19,11; 100,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,8; 42,24</t>
+          <t>-43,79; 38,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,2; 116,77</t>
+          <t>-31,52; 139,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-81,44; 270,56</t>
+          <t>-80,7; 298,53</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 12,69</t>
+          <t>-0,4; 12,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 12,46</t>
+          <t>0,39; 12,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 4,48</t>
+          <t>-5,89; 5,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,9; 1,05</t>
+          <t>-12,29; 0,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 101,69</t>
+          <t>-2,89; 94,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 107,5</t>
+          <t>2,32; 107,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,0; 40,29</t>
+          <t>-34,46; 47,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,66; 9,19</t>
+          <t>-61,38; 6,57</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 12,89</t>
+          <t>-2,06; 13,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 6,71</t>
+          <t>-5,41; 7,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 4,13</t>
+          <t>-7,57; 3,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 42,23</t>
+          <t>1,04; 40,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,88; 106,1</t>
+          <t>-12,62; 105,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,19; 65,08</t>
+          <t>-33,09; 73,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-47,93; 43,79</t>
+          <t>-46,88; 41,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,55; 324,88</t>
+          <t>3,85; 320,18</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 4,97</t>
+          <t>-6,61; 4,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 12,88</t>
+          <t>1,72; 12,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 9,32</t>
+          <t>-3,63; 8,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 6,81</t>
+          <t>-4,68; 7,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,86; 55,82</t>
+          <t>-43,42; 47,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,96; 201,23</t>
+          <t>13,04; 206,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,29; 85,9</t>
+          <t>-22,91; 89,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,16; 87,15</t>
+          <t>-33,08; 91,62</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 6,41</t>
+          <t>0,26; 6,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 7,01</t>
+          <t>0,52; 6,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,36</t>
+          <t>-2,21; 3,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 15,36</t>
+          <t>-2,72; 14,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,03; 50,72</t>
+          <t>1,76; 54,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 60,98</t>
+          <t>3,73; 56,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 28,76</t>
+          <t>-15,59; 31,91</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,49; 117,94</t>
+          <t>-18,74; 109,7</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 10,79</t>
+          <t>-3,86; 10,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 5,26</t>
+          <t>-8,95; 6,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 9,1</t>
+          <t>-4,63; 8,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 8,61</t>
+          <t>-22,56; 7,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,11; 100,25</t>
+          <t>-23,04; 90,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-43,79; 38,34</t>
+          <t>-42,18; 54,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 139,67</t>
+          <t>-38,84; 116,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-80,7; 298,53</t>
+          <t>-77,44; 241,2</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 12,03</t>
+          <t>0,26; 12,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,39; 12,18</t>
+          <t>0,43; 12,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 5,2</t>
+          <t>-6,22; 4,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,29; 0,43</t>
+          <t>-12,9; 0,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 94,27</t>
+          <t>0,8; 100,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 107,23</t>
+          <t>2,52; 112,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-34,46; 47,5</t>
+          <t>-36,29; 40,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,38; 6,57</t>
+          <t>-66,51; 6,58</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 13,26</t>
+          <t>-1,24; 13,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 7,74</t>
+          <t>-5,9; 7,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 3,85</t>
+          <t>-7,94; 4,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 40,94</t>
+          <t>1,93; 41,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 105,54</t>
+          <t>-7,48; 118,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 73,32</t>
+          <t>-34,9; 72,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,88; 41,07</t>
+          <t>-49,26; 49,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 320,18</t>
+          <t>7,95; 283,61</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 4,51</t>
+          <t>-5,88; 4,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 12,98</t>
+          <t>0,9; 12,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 8,76</t>
+          <t>-3,19; 9,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 7,34</t>
+          <t>-4,8; 7,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,42; 47,07</t>
+          <t>-41,92; 45,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,04; 206,62</t>
+          <t>7,12; 206,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-22,91; 89,17</t>
+          <t>-20,52; 95,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-33,08; 91,62</t>
+          <t>-36,48; 97,4</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 6,87</t>
+          <t>0,21; 6,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 6,54</t>
+          <t>0,55; 6,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,65</t>
+          <t>-2,56; 3,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 14,44</t>
+          <t>-2,53; 14,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 54,34</t>
+          <t>0,72; 51,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 56,25</t>
+          <t>3,73; 58,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-15,59; 31,91</t>
+          <t>-18,02; 33,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 109,7</t>
+          <t>-18,05; 112,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-11,59%</t>
+          <t>-1,79%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 10,12</t>
+          <t>-3,54; 11,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 6,79</t>
+          <t>-9,51; 5,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 8,39</t>
+          <t>-4,35; 8,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 7,98</t>
+          <t>-21,25; 8,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,04; 90,69</t>
+          <t>-20,11; 104,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-42,18; 54,4</t>
+          <t>-43,8; 42,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-38,84; 116,54</t>
+          <t>-37,2; 116,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-77,44; 241,2</t>
+          <t>-79,02; 293,16</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,49</t>
+          <t>-4,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-36,82%</t>
+          <t>-32,27%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 12,69</t>
+          <t>0,38; 12,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 12,19</t>
+          <t>-0,06; 12,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 4,8</t>
+          <t>-6,66; 4,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 0,53</t>
+          <t>-10,88; 2,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 100,72</t>
+          <t>2,07; 101,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 112,0</t>
+          <t>-1,27; 107,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-36,29; 40,96</t>
+          <t>-39,0; 40,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-66,51; 6,58</t>
+          <t>-60,03; 19,24</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,92</t>
+          <t>5,97</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 13,17</t>
+          <t>-1,84; 12,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 7,32</t>
+          <t>-5,57; 6,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 4,64</t>
+          <t>-8,32; 4,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 41,01</t>
+          <t>-2,06; 14,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,48; 118,81</t>
+          <t>-10,88; 106,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 72,99</t>
+          <t>-35,19; 65,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-49,26; 49,51</t>
+          <t>-47,93; 43,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,95; 283,61</t>
+          <t>-10,58; 101,02</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>12,92%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 4,26</t>
+          <t>-6,3; 4,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 12,73</t>
+          <t>1,25; 12,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 9,87</t>
+          <t>-3,42; 9,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 7,55</t>
+          <t>-4,76; 7,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 45,18</t>
+          <t>-41,86; 55,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 206,12</t>
+          <t>8,96; 201,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 95,03</t>
+          <t>-21,29; 85,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,48; 97,4</t>
+          <t>-33,1; 92,63</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 6,64</t>
+          <t>0,31; 6,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,76</t>
+          <t>0,42; 7,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 3,77</t>
+          <t>-2,84; 3,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 14,72</t>
+          <t>-4,09; 4,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 51,27</t>
+          <t>2,03; 50,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 58,86</t>
+          <t>2,98; 60,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 33,27</t>
+          <t>-18,73; 28,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 112,29</t>
+          <t>-24,68; 36,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2003-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2003-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>3,25</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,13</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-8,59%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,35%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-1,79%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>3.24819134569174</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.508146021067</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.129083231553611</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.1854524094742599</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2220891351558647</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.08592578486806067</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.2235028507962978</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.01790835697385683</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,54; 11,54</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,51; 5,74</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,35; 8,47</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-21,25; 8,27</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-20,11; 104,59</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-43,8; 42,24</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-37,2; 116,77</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-79,02; 293,16</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.536486600754614</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.514721699300486</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.346963041182272</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-21.25047950296371</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2011098134445481</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.4380442651937628</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.3720461471223225</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.7902479396256893</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.53668655828244</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.739602078043294</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.46755909492377</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>8.271685497399094</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.045856004495948</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.4224143813490074</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.167746159470893</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>2.931558634455794</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,17</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>6,05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,85</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,69</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>40,17%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>43,19%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-5,8%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-32,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,38; 12,69</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-0,06; 12,46</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-6,66; 4,48</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-10,88; 2,04</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,07; 101,69</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-1,27; 107,5</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-39,0; 40,29</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-60,03; 19,24</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>6.170144998622473</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6.047634325108215</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.8517435061675044</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-4.692918892961957</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.4016897049281982</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.4319075126854475</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.05804948281752061</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.3227270455841603</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,87</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,72</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,97</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>38,84%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-13,67%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33,26%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.3815835848010733</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-0.05820631454778882</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-6.660612612309912</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-10.88484477273173</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.02074983840674834</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.01274818912898312</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3900075832455723</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6003468611045129</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-1,84; 12,89</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,57; 6,71</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-8,32; 4,13</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-2,06; 14,16</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-10,88; 106,1</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-35,19; 65,08</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-47,93; 43,79</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-10,58; 101,02</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>12.68594202999324</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>12.4625620163245</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.48495064968977</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.035570628471242</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.016917911245163</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.075015559295452</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.4028784849516064</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1923709060906108</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,05</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-6,12%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>79,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12,92%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>5.868935979652131</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.7225225347967851</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-1.810602036213074</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.965374669174447</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.3884402305767874</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.05335257883920244</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.136733683798874</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.3326378155101121</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-6,3; 4,97</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,25; 12,88</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-3,42; 9,32</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,76; 7,03</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-41,86; 55,82</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,96; 201,23</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-21,29; 85,9</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-33,1; 92,63</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-1.836523194603862</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.573856131536141</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-8.318113334508853</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.06091504409495</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1088091265501242</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.351873056031407</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.4793056637662589</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.105808215833704</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>12.89175194700081</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.707747791592279</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.125218121941626</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>14.16008883557174</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.061005128109234</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.6508236726679065</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.4379068941396386</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.01022235440056</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.745522378082919</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>7.045308521927495</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>2.621369355805894</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.426303462484418</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.06118919255750452</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.7929882659484759</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.1960639730218237</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.1291993441501182</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-6.304274982046499</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>1.252572540854119</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.4239171706175</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.759189623617191</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4186154320383492</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.089640854048867</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.212903732546625</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3309761474808481</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.974350441099413</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>12.88125326355821</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>9.318416804285564</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.025315773795772</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5582123301114215</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>2.012343119076482</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.858953477345641</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.9263413233851989</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3,32</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,34</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>23,35%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>27,2%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>0,31; 6,41</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,42; 7,01</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-2,84; 3,36</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,09; 4,08</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,03; 50,72</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,98; 60,98</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-18,73; 28,76</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-24,68; 36,28</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>3.324628704364965</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.587748087187986</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.5383522527819762</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.3360304614951709</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.233455010993409</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.2719654616831852</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.04150978807649428</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.02440086572934767</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.3072120989258446</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.4246161913253664</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-2.838543395074778</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.086471349054026</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0.02030353417798412</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.02984557801453875</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.1872563844705683</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2467927710540574</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>6.407003577669854</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.006575714000219</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.363627043481517</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.080924738151556</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.5071966875469238</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.6098338520037379</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.287550788088451</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3627528755919204</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
